--- a/光伏配储项目/电价数据/2026/双岗站.xlsx
+++ b/光伏配储项目/电价数据/2026/双岗站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.54259</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7730199999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.61011</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58939</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.53947</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5768799999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43034</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44598</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.11053</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12139</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05763</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10014</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15332</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05021</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.47663</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.71261</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14608</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21438</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22815</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21727</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.12502</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53647</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.63501</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.47778</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73284</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6166699999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43209</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6591900000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.76927</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.10528</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.23822</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.9384199999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.13006</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.18719</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.37097</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58876</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.64159</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.38884</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.11357</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86676</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79691</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75782</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52064</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47303</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42557</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7099500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.75917</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8694299999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91386</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49413</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5156799999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50337</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50366</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48582</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8972100000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.82857</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38747</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49406</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7660399999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.98109</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.9062899999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85824</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70231</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.98188</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07754</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05744</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47351</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5398200000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5299199999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8860399999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.64225</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7837499999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.81296</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16762</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.20428</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86573</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.21266</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.11395</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.26824</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09923</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65313</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90222</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.00816</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.80075</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.76042</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45149</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78527</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80175</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42861</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44439</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50858</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48663</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49018</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47274</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44443</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5396</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82968</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.57974</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72602</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81276</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.54645</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.50504</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81738</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7698200000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6638099999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60193</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49695</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5083299999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56932</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59335</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.53967</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.55964</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27321</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61766</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.56441</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50736</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.63367</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6046699999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.60245</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49282</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.49636</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61203</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.65596</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56314</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7810499999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.64964</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47908</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6131599999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34201</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52891</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49166</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44928</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41445</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65106</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.7406200000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.49149</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7536900000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6027400000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48122</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49603</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47496</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51837</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.58761</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.45421</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.57859</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48161</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46653</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.41026</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32026</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20464</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22763</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22738</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.16025</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.16774</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17282</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.02678</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21902</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.17002</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22087</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.03203</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.02574</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00133</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.62273</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48968</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34582</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.60549</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10264</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22783</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.06004</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.23043</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.08198</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.08026000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33242</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45587</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78527</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91422</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86291</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88754</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18712</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86682</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33088</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03294</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308200000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.49418</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49318</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39992</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20703</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62188</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44977</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5657799999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58769</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7151000000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8773200000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5593899999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.83184</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85768</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8749600000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.64555</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6619299999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60111</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.20518</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34889</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91462</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18374</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19834</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25467</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5501900000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87478</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.46406</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14766</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6917300000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78224</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64281</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.52542</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49407</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40877</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40717</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48925</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.53286</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.24912</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24901</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16099</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.00439</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25415</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.55026</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.80004</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31206</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.26745</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14471</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.12613</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14097</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13337</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.12674</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24612</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13257</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24589</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.21574</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.12185</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09731000000000001</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10844</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12504</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19297</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26451</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42141</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33821</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27376</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23907</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35167</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48437</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.28106</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6504099999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.21928</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.57609</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.46115</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.8776499999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.42886</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.67884</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69241</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.6856100000000001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6304299999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.53606</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50566</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3236</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40774</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34505</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6523</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.73515</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.43775</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33726</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.21622</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.23064</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6385599999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5967</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59884</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8021699999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7261299999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48433</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3528</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5422100000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48599</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6378200000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.42557</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.51935</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.47085</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.51881</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51773</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.59838</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6563600000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.97992</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46723</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.51623</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6416799999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7573200000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.83726</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58705</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.73721</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.6404299999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.51274</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.75917</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7664800000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6192799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6679400000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44878</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44608</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51788</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21042</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43126</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34152</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.27002</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.1968</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25532</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10642</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25515</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03666</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18788</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24522</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23841</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33122</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.25929</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.26131</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.25992</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.25818</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17615</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01413</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00109</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14575</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02014</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01519</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04269</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04855</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04819</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02447</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02906</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03909000000000001</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01866</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03628</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20054</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32982</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.74473</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6241100000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43545</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7159500000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8625700000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87193</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83475</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10606</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21791</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25636</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00281</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00247</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.54707</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.80576</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.7825800000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7908099999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.3723</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98287</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.78346</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.84651</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.81428</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84135</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8439099999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94098</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.77654</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8101699999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7789199999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36733</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47501</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.62703</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.70037</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5875199999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.4645899999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.78037</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6275700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43468</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49671</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34606</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5894299999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.78716</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.57313</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52552</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5869800000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47677</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8151799999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.54965</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.48562</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54511</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.59411</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8327</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.74722</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5880599999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24133</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35872</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46338</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.52839</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.7371599999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.67345</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.75547</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.70636</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49953</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5840299999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6448400000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.49159</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8020700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7886299999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.00565</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8812000000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.8146599999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8029299999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44478</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36308</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.22465</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.19946</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16186</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.13022</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.22376</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.17062</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.25398</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.15759</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.21965</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.23512</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.50805</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43212</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36948</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9746699999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6045499999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.50932</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46698</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.53498</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.49272</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36204</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17446</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14418</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19635</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14019</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04184</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12759</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.16626</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14631</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.21256</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22423</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26075</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15251</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19551</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38647</v>
       </c>
     </row>
   </sheetData>
